--- a/data/trans_camb/POLIPATOLOGIA_Lim_5-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/POLIPATOLOGIA_Lim_5-Habitat-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 1,57</t>
+          <t>-2,29; 1,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,9; 7,73</t>
+          <t>2,74; 7,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 4,44</t>
+          <t>-2,07; 4,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,69; 9,46</t>
+          <t>2,82; 10,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 2,17</t>
+          <t>-1,75; 2,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,16; 8,34</t>
+          <t>4,01; 8,37</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-52,26; 56,82</t>
+          <t>-49,85; 51,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>57,89; 281,81</t>
+          <t>54,88; 279,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-21,39; 57,64</t>
+          <t>-19,22; 58,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26,85; 123,9</t>
+          <t>25,4; 136,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-20,99; 38,16</t>
+          <t>-23,01; 39,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>58,27; 158,07</t>
+          <t>53,11; 159,54</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 1,24</t>
+          <t>-2,09; 1,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 4,03</t>
+          <t>-1,2; 4,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 2,09</t>
+          <t>-2,92; 2,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,17; 8,07</t>
+          <t>3,34; 8,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 0,92</t>
+          <t>-1,99; 1,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 5,19</t>
+          <t>0,06; 5,29</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-46,85; 49,48</t>
+          <t>-48,45; 41,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-21,47; 145,11</t>
+          <t>-28,69; 148,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-30,28; 28,11</t>
+          <t>-29,53; 29,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31,85; 108,26</t>
+          <t>31,31; 110,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-30,13; 16,83</t>
+          <t>-29,41; 20,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,73; 95,4</t>
+          <t>2,25; 95,6</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 0,89</t>
+          <t>-2,77; 0,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,23; 4,94</t>
+          <t>0,39; 5,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 2,16</t>
+          <t>-3,39; 2,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 5,42</t>
+          <t>-4,52; 5,27</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 0,92</t>
+          <t>-2,5; 0,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 4,42</t>
+          <t>-1,1; 4,65</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-60,23; 35,29</t>
+          <t>-58,46; 41,3</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,53; 170,01</t>
+          <t>4,02; 186,87</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-35,24; 31,19</t>
+          <t>-35,16; 37,29</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-41,81; 69,53</t>
+          <t>-45,97; 69,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-37,86; 17,86</t>
+          <t>-36,19; 16,86</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-12,46; 83,45</t>
+          <t>-12,73; 85,52</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 1,63</t>
+          <t>-2,01; 1,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,17; 5,17</t>
+          <t>1,02; 5,16</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 1,93</t>
+          <t>-3,43; 2,24</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,04; 8,03</t>
+          <t>1,75; 8,35</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 1,32</t>
+          <t>-2,04; 1,4</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,51; 6,37</t>
+          <t>2,36; 6,28</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-42,25; 57,45</t>
+          <t>-42,06; 60,3</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>20,82; 188,82</t>
+          <t>21,09; 198,29</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-28,86; 22,0</t>
+          <t>-29,21; 24,3</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12,08; 87,36</t>
+          <t>14,69; 91,72</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-26,32; 20,02</t>
+          <t>-25,63; 22,48</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,47; 99,25</t>
+          <t>27,97; 96,29</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 0,46</t>
+          <t>-1,27; 0,53</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,39; 4,26</t>
+          <t>1,58; 4,26</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 1,14</t>
+          <t>-1,62; 1,25</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,63; 6,33</t>
+          <t>1,94; 6,27</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 0,54</t>
+          <t>-1,19; 0,46</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,53; 5,01</t>
+          <t>2,5; 5,06</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-31,8; 15,34</t>
+          <t>-31,62; 18,63</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>36,77; 134,22</t>
+          <t>43,31; 140,62</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-16,37; 13,27</t>
+          <t>-16,7; 14,98</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>17,52; 72,53</t>
+          <t>22,68; 72,69</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-17,79; 8,71</t>
+          <t>-17,1; 7,62</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>37,56; 82,08</t>
+          <t>37,83; 83,86</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/POLIPATOLOGIA_Lim_5-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/POLIPATOLOGIA_Lim_5-Habitat-trans_camb.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5,36</t>
+          <t>5,15</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,59</t>
+          <t>7,45</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,21</t>
+          <t>6,43</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 1,54</t>
+          <t>-2,32; 1,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,74; 7,84</t>
+          <t>2,62; 7,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 4,28</t>
+          <t>-2,33; 4,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,82; 10,01</t>
+          <t>4,16; 10,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 2,14</t>
+          <t>-1,46; 2,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,01; 8,37</t>
+          <t>4,37; 8,33</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>145,6%</t>
+          <t>139,86%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>100,55%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-49,85; 51,62</t>
+          <t>-49,08; 57,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>54,88; 279,71</t>
+          <t>52,07; 293,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-19,22; 58,24</t>
+          <t>-20,61; 57,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25,4; 136,67</t>
+          <t>36,96; 138,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-23,01; 39,6</t>
+          <t>-21,27; 40,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>53,11; 159,54</t>
+          <t>56,63; 154,8</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,98</t>
+          <t>3,1</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,76</t>
+          <t>5,42</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,35</t>
+          <t>4,28</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 1,03</t>
+          <t>-2,01; 1,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 4,1</t>
+          <t>1,26; 4,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 2,28</t>
+          <t>-3,14; 1,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,34; 8,24</t>
+          <t>2,69; 7,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 1,04</t>
+          <t>-2,09; 1,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,06; 5,29</t>
+          <t>2,63; 5,92</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>70,52%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-48,45; 41,8</t>
+          <t>-48,04; 50,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-28,69; 148,99</t>
+          <t>25,27; 196,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-29,53; 29,93</t>
+          <t>-31,65; 25,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31,31; 110,86</t>
+          <t>26,63; 100,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-29,41; 20,86</t>
+          <t>-31,14; 20,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,25; 95,6</t>
+          <t>36,48; 112,06</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2,81</t>
+          <t>2,62</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,54</t>
+          <t>4,59</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,38</t>
+          <t>3,6</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 0,95</t>
+          <t>-2,97; 0,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,39; 5,3</t>
+          <t>0,46; 5,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 2,4</t>
+          <t>-3,25; 2,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 5,27</t>
+          <t>1,66; 7,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 0,86</t>
+          <t>-2,32; 1,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 4,65</t>
+          <t>1,79; 5,38</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>70,8%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>55,14%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>59,5%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-58,46; 41,3</t>
+          <t>-61,56; 36,53</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,02; 186,87</t>
+          <t>7,13; 197,51</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-35,16; 37,29</t>
+          <t>-34,36; 35,8</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-45,97; 69,0</t>
+          <t>15,47; 108,43</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-36,19; 16,86</t>
+          <t>-35,21; 20,09</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-12,73; 85,52</t>
+          <t>26,47; 105,64</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3,25</t>
+          <t>3,18</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5,16</t>
+          <t>5,79</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,39</t>
+          <t>4,6</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 1,59</t>
+          <t>-1,84; 1,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,02; 5,16</t>
+          <t>1,14; 5,01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 2,24</t>
+          <t>-3,6; 2,21</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,75; 8,35</t>
+          <t>3,03; 8,57</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 1,4</t>
+          <t>-1,99; 1,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,36; 6,28</t>
+          <t>2,87; 6,22</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>54,72%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>63,11%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-42,06; 60,3</t>
+          <t>-41,01; 65,14</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>21,09; 198,29</t>
+          <t>20,67; 185,37</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-29,21; 24,3</t>
+          <t>-30,06; 23,73</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14,69; 91,72</t>
+          <t>25,23; 95,57</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-25,63; 22,48</t>
+          <t>-24,57; 22,3</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,97; 96,29</t>
+          <t>34,41; 96,57</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3,09</t>
+          <t>3,41</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4,67</t>
+          <t>5,76</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,96</t>
+          <t>4,64</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 0,53</t>
+          <t>-1,4; 0,49</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,58; 4,26</t>
+          <t>2,48; 4,49</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 1,25</t>
+          <t>-1,81; 1,27</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,94; 6,27</t>
+          <t>4,38; 7,17</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 0,46</t>
+          <t>-1,24; 0,46</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,5; 5,06</t>
+          <t>3,79; 5,59</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>61,08%</t>
+          <t>71,71%</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-31,62; 18,63</t>
+          <t>-34,02; 16,63</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>43,31; 140,62</t>
+          <t>59,07; 148,09</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-16,7; 14,98</t>
+          <t>-17,81; 14,7</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>22,68; 72,69</t>
+          <t>42,01; 84,3</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-17,1; 7,62</t>
+          <t>-17,89; 7,54</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>37,83; 83,86</t>
+          <t>54,68; 92,21</t>
         </is>
       </c>
     </row>
